--- a/計量票入力図/計量票入力図.xlsx
+++ b/計量票入力図/計量票入力図.xlsx
@@ -5,16 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\!!ユーザー\き-共和紙料\AI用資料\計量票入力図\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\!!ユーザー\き-共和紙料\AI用資料\ScaleLinkProj\計量票入力図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D338A0E8-AE1A-43E4-98B9-B5028AB7B67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6467C61-D3FA-4474-B9EB-FE4BF8E7D4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40395" yWindow="5115" windowWidth="30420" windowHeight="23205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-45" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$BJ$34</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -257,23 +261,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>145348</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>4513</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>142876</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>47123</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3A3DC79-CD83-2F9D-BBCD-971A5AEC85A8}"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{983981B1-8C21-EAB8-CB72-4E56EA2DD1D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -282,15 +286,21 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2857500" y="3067050"/>
-          <a:ext cx="5145973" cy="4133850"/>
+          <a:off x="3100138" y="2619376"/>
+          <a:ext cx="5519485" cy="3495674"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -301,23 +311,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>3440</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:col>64</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>86</xdr:col>
+      <xdr:colOff>50098</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84E0206D-87C2-2A42-8326-08DB8E32AC93}"/>
+        <xdr:cNvPr id="28" name="図 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3A3DC79-CD83-2F9D-BBCD-971A5AEC85A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -326,7 +336,51 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15382875" y="3533775"/>
+          <a:ext cx="5145973" cy="4133850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>3440</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84E0206D-87C2-2A42-8326-08DB8E32AC93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -376,7 +430,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -539,16 +593,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>47624</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>47624</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>209550</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -563,7 +617,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2905124" y="3952875"/>
+          <a:off x="2666999" y="3867150"/>
           <a:ext cx="476250" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -627,7 +681,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -654,12 +708,12 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>204940</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>200024</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>180974</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>181863</xdr:rowOff>
     </xdr:to>
@@ -679,8 +733,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="2773788" y="6079852"/>
-          <a:ext cx="1048638" cy="3328834"/>
+          <a:off x="2459463" y="5308327"/>
+          <a:ext cx="2134488" cy="3786034"/>
         </a:xfrm>
         <a:prstGeom prst="curvedConnector2">
           <a:avLst/>
@@ -715,16 +769,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>200024</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>200024</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>180974</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>180974</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -739,7 +793,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4724399" y="6924675"/>
+          <a:off x="5181599" y="5838825"/>
           <a:ext cx="476250" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -803,7 +857,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -853,7 +907,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -878,16 +932,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -902,7 +956,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5381624" y="6905625"/>
+          <a:off x="5943599" y="5829300"/>
           <a:ext cx="476250" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1004,16 +1058,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>295274</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>228598</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>57151</xdr:colOff>
+      <xdr:colOff>57149</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1031,8 +1085,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1">
-          <a:off x="4838700" y="7981949"/>
-          <a:ext cx="2428875" cy="866776"/>
+          <a:off x="4581524" y="7724774"/>
+          <a:ext cx="3505200" cy="304801"/>
         </a:xfrm>
         <a:prstGeom prst="curvedConnector2">
           <a:avLst/>
@@ -1241,7 +1295,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1276,7 +1330,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1302,16 +1356,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>47624</xdr:colOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>209549</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>114299</xdr:colOff>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1326,7 +1380,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9096374" y="4105275"/>
+          <a:off x="9496424" y="4114800"/>
           <a:ext cx="1495425" cy="590550"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -1368,16 +1422,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>80962</xdr:colOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>190499</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1395,8 +1449,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="9844087" y="2781299"/>
-          <a:ext cx="823912" cy="1323975"/>
+          <a:off x="10244137" y="2781300"/>
+          <a:ext cx="423862" cy="1333500"/>
         </a:xfrm>
         <a:prstGeom prst="curvedConnector2">
           <a:avLst/>
@@ -1434,16 +1488,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>33</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>242888</xdr:rowOff>
+      <xdr:rowOff>161924</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>233362</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1461,8 +1515,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000" flipV="1">
-          <a:off x="8039100" y="4400550"/>
-          <a:ext cx="1057275" cy="681038"/>
+          <a:off x="8515350" y="4410074"/>
+          <a:ext cx="981075" cy="366713"/>
         </a:xfrm>
         <a:prstGeom prst="curvedConnector3">
           <a:avLst>
@@ -1502,16 +1556,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>180974</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>180974</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>180974</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1526,7 +1580,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7562849" y="4933950"/>
+          <a:off x="8039099" y="4629150"/>
           <a:ext cx="476250" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1638,10 +1692,10 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>147638</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:rowOff>61913</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>47624</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>190501</xdr:rowOff>
@@ -1662,8 +1716,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="2114550" y="4100513"/>
-          <a:ext cx="790574" cy="42863"/>
+          <a:off x="2114550" y="4014788"/>
+          <a:ext cx="552449" cy="128588"/>
         </a:xfrm>
         <a:prstGeom prst="curvedConnector3">
           <a:avLst>
@@ -1766,16 +1820,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>76199</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>276225</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>76199</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>276225</xdr:rowOff>
+      <xdr:colOff>238124</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>238124</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1790,7 +1844,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6029324" y="6886575"/>
+          <a:off x="6667499" y="5800725"/>
           <a:ext cx="476250" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1829,16 +1883,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>276224</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:rowOff>200026</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1855,12 +1909,15 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm rot="16200000" flipH="1">
-          <a:off x="5967412" y="7481887"/>
-          <a:ext cx="1104901" cy="504826"/>
-        </a:xfrm>
-        <a:prstGeom prst="curvedConnector2">
-          <a:avLst/>
+        <a:xfrm rot="5400000">
+          <a:off x="5743575" y="7124701"/>
+          <a:ext cx="2190751" cy="133349"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector4">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 36522"/>
+            <a:gd name="adj2" fmla="val 271430"/>
+          </a:avLst>
         </a:prstGeom>
         <a:ln w="73025">
           <a:tailEnd type="triangle"/>
@@ -2550,8 +2607,19 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="61" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
+  <pageSetup paperSize="8" scale="96" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0204AB33-8F77-4FF9-B06F-5F4EF431AF2B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>